--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6446,10 +6446,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1736026</v>
+        <v>99497515</v>
       </c>
       <c r="B52" t="n">
-        <v>76579</v>
+        <v>91852</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6458,50 +6458,52 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4202</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sacc.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Umeå, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752996.3043383379</v>
+        <v>753176</v>
       </c>
       <c r="R52" t="n">
-        <v>7095001.956038775</v>
+        <v>7095564</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6525,22 +6527,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2012-11-23</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6549,39 +6551,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>i gräsmattan, vidskogsvägen</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr"/>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Tonje Lindmark</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Tonje Lindmark</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>111773558</v>
+        <v>1736026</v>
       </c>
       <c r="B53" t="n">
-        <v>105155</v>
+        <v>76579</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6590,57 +6582,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220107</v>
+        <v>4202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Geoglossum umbratile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sacc.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752974</v>
+        <v>752996.3043383379</v>
       </c>
       <c r="R53" t="n">
-        <v>7095000</v>
+        <v>7095001.956038775</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6664,12 +6649,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2012-09-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6678,22 +6673,151 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>i gräsmattan, vidskogsvägen</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr"/>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>111773558</v>
+      </c>
+      <c r="B54" t="n">
+        <v>105155</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S54" t="n">
+        <v>50</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>Bertil Brånin</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>Bertil Brånin</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6570,10 +6570,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1736026</v>
+        <v>120533224</v>
       </c>
       <c r="B53" t="n">
-        <v>76579</v>
+        <v>91862</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6582,50 +6582,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4202</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sacc.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752996.3043383379</v>
+        <v>753603</v>
       </c>
       <c r="R53" t="n">
-        <v>7095001.956038775</v>
+        <v>7095544</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6649,22 +6640,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2012-11-23</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga sågad, basen mot stående tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6676,36 +6662,25 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>i gräsmattan, vidskogsvägen</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr"/>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111773558</v>
+        <v>120533247</v>
       </c>
       <c r="B54" t="n">
-        <v>105155</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6714,57 +6689,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220107</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752974</v>
+        <v>753535</v>
       </c>
       <c r="R54" t="n">
-        <v>7095000</v>
+        <v>7095507</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6788,12 +6747,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6802,22 +6761,2863 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120533219</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>753126</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7095398</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre födohack</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120533227</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>753299</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7095581</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Under tunn tallgren invid tall</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120533246</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>753598</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7095545</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120533214</v>
+      </c>
+      <c r="B58" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>753030</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7095366</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Tallgren</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallgren</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120533220</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>753443</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7095503</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre födohack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120533222</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91839</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>753304</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7095588</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Cirka 20 fk under nedbruten talllåga vid grop</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120533218</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>753599</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7095609</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120533229</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>753282</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7095457</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Under längre tallåga vid stigen</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120533211</v>
+      </c>
+      <c r="B63" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>753042</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7095398</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Undersida tunn tallåga</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120533221</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>753310</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7095459</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre födohack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120533226</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>753301</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7095541</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i grop</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120533245</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>753600</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7095611</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120533232</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>753412</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7095506</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Under väldigt tunn tallåga</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120533228</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>753100</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7095391</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Under tallåga i slänt</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120533210</v>
+      </c>
+      <c r="B69" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>752965</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7095301</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Undersidan tunn tallgren i mossa</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120533238</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>753395</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7095506</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120533252</v>
+      </c>
+      <c r="B71" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>753282</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7095460</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Undersidan tall, växte mest på förnarester, såg den när jag lyfte lågan.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Silverlåga på sand invid stig</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Silverlåga på sand invid stig</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120533225</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>753309</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7095549</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga i mossa</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120533244</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>753469</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7095664</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Växte under tallåga, bilder</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120533231</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>753358</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7095463</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Under tunn tallgren i mossa</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120533239</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>752996</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7095304</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120533237</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>753312</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7095593</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120533241</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kullaheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>753412</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7095620</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1736026</v>
+      </c>
+      <c r="B78" t="n">
+        <v>76579</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4202</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Svart jordtunga</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Geoglossum umbratile</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>752996.3043383379</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7095001.956038775</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2012-09-22</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>i gräsmattan, vidskogsvägen</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>111773558</v>
+      </c>
+      <c r="B79" t="n">
+        <v>105155</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S79" t="n">
+        <v>50</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
           <t>Bertil Brånin</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AX79" t="inlineStr">
         <is>
           <t>Bertil Brånin</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -6570,10 +6570,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120533224</v>
+        <v>120533220</v>
       </c>
       <c r="B53" t="n">
-        <v>91862</v>
+        <v>57336</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6582,38 +6582,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753603</v>
+        <v>753443</v>
       </c>
       <c r="R53" t="n">
-        <v>7095544</v>
+        <v>7095503</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6650,7 +6655,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Under tunn talllåga sågad, basen mot stående tall</t>
+          <t>Äldre födohack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6661,6 +6666,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6677,10 +6702,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120533247</v>
+        <v>120533237</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6689,38 +6714,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753535</v>
+        <v>753312</v>
       </c>
       <c r="R54" t="n">
-        <v>7095507</v>
+        <v>7095593</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6808,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120533219</v>
+        <v>120533214</v>
       </c>
       <c r="B55" t="n">
-        <v>57336</v>
+        <v>89650</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,39 +6824,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753126</v>
+        <v>753030</v>
       </c>
       <c r="R55" t="n">
-        <v>7095398</v>
+        <v>7095366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6862,11 +6886,6 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre födohack</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6888,12 +6907,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Tallhögstubbe</t>
+          <t>Tallgren</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallhögstubbe</t>
+          <t>Pinus sylvestris # Tallgren</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6911,7 +6930,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120533227</v>
+        <v>120533228</v>
       </c>
       <c r="B56" t="n">
         <v>91862</v>
@@ -6951,10 +6970,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753299</v>
+        <v>753100</v>
       </c>
       <c r="R56" t="n">
-        <v>7095581</v>
+        <v>7095391</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6991,7 +7010,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Under tunn tallgren invid tall</t>
+          <t>Under tallåga i slänt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7018,10 +7037,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120533246</v>
+        <v>120533252</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7030,25 +7049,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7058,10 +7077,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753598</v>
+        <v>753282</v>
       </c>
       <c r="R57" t="n">
-        <v>7095545</v>
+        <v>7095460</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7096,14 +7115,40 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Undersidan tall, växte mest på förnarester, såg den när jag lyfte lågan.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Silverlåga på sand invid stig</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Silverlåga på sand invid stig</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7120,10 +7165,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120533214</v>
+        <v>120533225</v>
       </c>
       <c r="B58" t="n">
-        <v>89650</v>
+        <v>91862</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7132,25 +7177,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7160,10 +7205,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753030</v>
+        <v>753309</v>
       </c>
       <c r="R58" t="n">
-        <v>7095366</v>
+        <v>7095549</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7198,6 +7243,11 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga i mossa</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7206,26 +7256,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Tallgren</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallgren</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7242,10 +7272,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120533220</v>
+        <v>120533244</v>
       </c>
       <c r="B59" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7254,43 +7284,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753443</v>
+        <v>753469</v>
       </c>
       <c r="R59" t="n">
-        <v>7095503</v>
+        <v>7095664</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7327,7 +7352,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre födohack</t>
+          <t>Växte under tallåga, bilder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7338,26 +7363,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7374,10 +7379,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120533222</v>
+        <v>120533239</v>
       </c>
       <c r="B60" t="n">
-        <v>91839</v>
+        <v>91881</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7386,30 +7391,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7418,10 +7423,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753304</v>
+        <v>752996</v>
       </c>
       <c r="R60" t="n">
-        <v>7095588</v>
+        <v>7095304</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7454,11 +7459,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Cirka 20 fk under nedbruten talllåga vid grop</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7485,10 +7485,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120533218</v>
+        <v>120533247</v>
       </c>
       <c r="B61" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7497,25 +7497,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753599</v>
+        <v>753535</v>
       </c>
       <c r="R61" t="n">
-        <v>7095609</v>
+        <v>7095507</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7587,10 +7587,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120533229</v>
+        <v>120533245</v>
       </c>
       <c r="B62" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7599,25 +7599,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753282</v>
+        <v>753600</v>
       </c>
       <c r="R62" t="n">
-        <v>7095457</v>
+        <v>7095611</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7663,11 +7663,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Under längre tallåga vid stigen</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7694,7 +7689,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120533211</v>
+        <v>120533210</v>
       </c>
       <c r="B63" t="n">
         <v>89650</v>
@@ -7734,10 +7729,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753042</v>
+        <v>752965</v>
       </c>
       <c r="R63" t="n">
-        <v>7095398</v>
+        <v>7095301</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7774,7 +7769,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Undersida tunn tallåga</t>
+          <t>Undersidan tunn tallgren i mossa</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7816,10 +7811,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120533221</v>
+        <v>120533227</v>
       </c>
       <c r="B64" t="n">
-        <v>57336</v>
+        <v>91862</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7828,43 +7823,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>4365</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753310</v>
+        <v>753299</v>
       </c>
       <c r="R64" t="n">
-        <v>7095459</v>
+        <v>7095581</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7901,7 +7891,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre födohack</t>
+          <t>Under tunn tallgren invid tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7912,26 +7902,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7948,7 +7918,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120533226</v>
+        <v>120533232</v>
       </c>
       <c r="B65" t="n">
         <v>91862</v>
@@ -7981,17 +7951,21 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753301</v>
+        <v>753412</v>
       </c>
       <c r="R65" t="n">
-        <v>7095541</v>
+        <v>7095506</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8028,7 +8002,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Under tunn tallåga i grop</t>
+          <t>Under väldigt tunn tallåga</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8055,10 +8029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120533245</v>
+        <v>120533226</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8067,25 +8041,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8095,10 +8069,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753600</v>
+        <v>753301</v>
       </c>
       <c r="R66" t="n">
-        <v>7095611</v>
+        <v>7095541</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8131,6 +8105,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i grop</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8157,10 +8136,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120533232</v>
+        <v>120533211</v>
       </c>
       <c r="B67" t="n">
-        <v>91862</v>
+        <v>89650</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8169,42 +8148,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753412</v>
+        <v>753042</v>
       </c>
       <c r="R67" t="n">
-        <v>7095506</v>
+        <v>7095398</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8241,7 +8216,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Under väldigt tunn tallåga</t>
+          <t>Undersida tunn tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8252,6 +8227,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8268,7 +8258,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120533228</v>
+        <v>120533231</v>
       </c>
       <c r="B68" t="n">
         <v>91862</v>
@@ -8301,17 +8291,21 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753100</v>
+        <v>753358</v>
       </c>
       <c r="R68" t="n">
-        <v>7095391</v>
+        <v>7095463</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8348,7 +8342,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Under tallåga i slänt</t>
+          <t>Under tunn tallgren i mossa</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8375,10 +8369,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120533210</v>
+        <v>120533238</v>
       </c>
       <c r="B69" t="n">
-        <v>89650</v>
+        <v>91850</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8391,34 +8385,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>752965</v>
+        <v>753395</v>
       </c>
       <c r="R69" t="n">
-        <v>7095301</v>
+        <v>7095506</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8453,11 +8451,6 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Undersidan tunn tallgren i mossa</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8466,21 +8459,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8497,10 +8475,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120533238</v>
+        <v>120533229</v>
       </c>
       <c r="B70" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8509,42 +8487,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753395</v>
+        <v>753282</v>
       </c>
       <c r="R70" t="n">
-        <v>7095506</v>
+        <v>7095457</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8577,6 +8551,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Under längre tallåga vid stigen</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8603,10 +8582,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120533252</v>
+        <v>120533221</v>
       </c>
       <c r="B71" t="n">
-        <v>89650</v>
+        <v>57336</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8619,34 +8598,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1962</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753282</v>
+        <v>753310</v>
       </c>
       <c r="R71" t="n">
-        <v>7095460</v>
+        <v>7095459</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8683,7 +8667,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Undersidan tall, växte mest på förnarester, såg den när jag lyfte lågan.</t>
+          <t>Äldre födohack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8692,7 +8676,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8708,12 +8691,12 @@
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>Silverlåga på sand invid stig</t>
+          <t>Tallhögstubbe</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverlåga på sand invid stig</t>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8731,10 +8714,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120533225</v>
+        <v>120533241</v>
       </c>
       <c r="B72" t="n">
-        <v>91862</v>
+        <v>91881</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8743,25 +8726,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4365</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8771,10 +8754,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753309</v>
+        <v>753412</v>
       </c>
       <c r="R72" t="n">
-        <v>7095549</v>
+        <v>7095620</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8807,11 +8790,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga i mossa</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8838,10 +8816,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120533244</v>
+        <v>120533219</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8850,38 +8828,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753469</v>
+        <v>753126</v>
       </c>
       <c r="R73" t="n">
-        <v>7095664</v>
+        <v>7095398</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8918,7 +8901,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Växte under tallåga, bilder</t>
+          <t>Äldre födohack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8929,6 +8912,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8945,10 +8948,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120533231</v>
+        <v>120533218</v>
       </c>
       <c r="B74" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8957,42 +8960,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753358</v>
+        <v>753599</v>
       </c>
       <c r="R74" t="n">
-        <v>7095463</v>
+        <v>7095609</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9025,11 +9024,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Under tunn tallgren i mossa</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9056,10 +9050,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120533239</v>
+        <v>120533222</v>
       </c>
       <c r="B75" t="n">
-        <v>91881</v>
+        <v>91839</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9068,30 +9062,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>6055</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9100,10 +9094,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>752996</v>
+        <v>753304</v>
       </c>
       <c r="R75" t="n">
-        <v>7095304</v>
+        <v>7095588</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9136,6 +9130,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Cirka 20 fk under nedbruten talllåga vid grop</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9162,10 +9161,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120533237</v>
+        <v>120533224</v>
       </c>
       <c r="B76" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9174,42 +9173,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753312</v>
+        <v>753603</v>
       </c>
       <c r="R76" t="n">
-        <v>7095593</v>
+        <v>7095544</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9242,6 +9237,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga sågad, basen mot stående tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9268,10 +9268,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120533241</v>
+        <v>120533246</v>
       </c>
       <c r="B77" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9280,25 +9280,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753412</v>
+        <v>753598</v>
       </c>
       <c r="R77" t="n">
-        <v>7095620</v>
+        <v>7095545</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14745,7 +14745,7 @@
         <v>127073715</v>
       </c>
       <c r="B126" t="n">
-        <v>88338</v>
+        <v>88406</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14745,7 +14745,7 @@
         <v>127073715</v>
       </c>
       <c r="B126" t="n">
-        <v>88406</v>
+        <v>88412</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14745,7 +14745,7 @@
         <v>127073715</v>
       </c>
       <c r="B126" t="n">
-        <v>88412</v>
+        <v>88413</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14745,7 +14745,7 @@
         <v>127073715</v>
       </c>
       <c r="B126" t="n">
-        <v>88413</v>
+        <v>88417</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>127074261</v>
       </c>
       <c r="B127" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>126953776</v>
       </c>
       <c r="B130" t="n">
-        <v>56613</v>
+        <v>56617</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>127009098</v>
       </c>
       <c r="B131" t="n">
-        <v>58488</v>
+        <v>58492</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14745,7 +14745,7 @@
         <v>127073715</v>
       </c>
       <c r="B126" t="n">
-        <v>88417</v>
+        <v>88419</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>127074261</v>
       </c>
       <c r="B127" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>126953776</v>
       </c>
       <c r="B130" t="n">
-        <v>56617</v>
+        <v>56619</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>127009098</v>
       </c>
       <c r="B131" t="n">
-        <v>58492</v>
+        <v>58494</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14745,7 +14745,7 @@
         <v>127073715</v>
       </c>
       <c r="B126" t="n">
-        <v>88419</v>
+        <v>88425</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14745,7 +14745,7 @@
         <v>127073715</v>
       </c>
       <c r="B126" t="n">
-        <v>88425</v>
+        <v>88428</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>127074261</v>
       </c>
       <c r="B127" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14979,15 +14979,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1736026</v>
+        <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>76579</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92648</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14995,43 +14990,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4202</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sacc.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>752996.3043383379</v>
+        <v>753512</v>
       </c>
       <c r="R128" t="n">
-        <v>7095001.956038775</v>
+        <v>7095557</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15058,22 +15044,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2012-11-23</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15085,95 +15066,63 @@
       <c r="AG128" t="b">
         <v>0</v>
       </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>i gräsmattan, vidskogsvägen</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr"/>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>111773558</v>
+        <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>105155</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92648</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220107</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>752974</v>
+        <v>753526</v>
       </c>
       <c r="R129" t="n">
-        <v>7095000</v>
+        <v>7095601</v>
       </c>
       <c r="S129" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15197,12 +15146,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15211,84 +15165,78 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126953776</v>
+        <v>128464803</v>
       </c>
       <c r="B130" t="n">
-        <v>56619</v>
+        <v>57833</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>208260</v>
+        <v>103021</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>trafikdödad</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>752974</v>
+        <v>753527</v>
       </c>
       <c r="R130" t="n">
-        <v>7095000</v>
+        <v>7095601</v>
       </c>
       <c r="S130" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15312,27 +15260,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Mörk med tydligt zig zag band - 72 cm.</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15341,29 +15284,33 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127009098</v>
+        <v>1736026</v>
       </c>
       <c r="B131" t="n">
-        <v>58494</v>
+        <v>76579</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15371,21 +15318,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>208245</v>
+        <v>4202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Geoglossum umbratile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -15393,32 +15340,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>752974</v>
+        <v>752996.3043383379</v>
       </c>
       <c r="R131" t="n">
-        <v>7095000</v>
+        <v>7095001.956038775</v>
       </c>
       <c r="S131" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15442,22 +15381,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2012-09-22</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2012-11-23</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15466,22 +15405,406 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>i gräsmattan, vidskogsvägen</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr"/>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>111773558</v>
+      </c>
+      <c r="B132" t="n">
+        <v>105155</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S132" t="n">
+        <v>50</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
           <t>Bertil Brånin</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
+      <c r="AX132" t="inlineStr">
         <is>
           <t>Bertil Brånin</t>
         </is>
       </c>
-      <c r="AY131" t="inlineStr"/>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>126953776</v>
+      </c>
+      <c r="B133" t="n">
+        <v>56619</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S133" t="n">
+        <v>50</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Mörk med tydligt zig zag band - 72 cm.</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>127009098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>58494</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S134" t="n">
+        <v>50</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>128464803</v>
       </c>
       <c r="B130" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>128464803</v>
       </c>
       <c r="B130" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AY140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15302,59 +15302,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1736026</v>
+        <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>76579</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92760</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4202</v>
+        <v>4365</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sacc.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>752996.3043383379</v>
+        <v>753313</v>
       </c>
       <c r="R131" t="n">
-        <v>7095001.956038775</v>
+        <v>7095539</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -15381,22 +15367,17 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2012-11-23</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Under tunn tallgren, kapad</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15408,95 +15389,67 @@
       <c r="AG131" t="b">
         <v>0</v>
       </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>i gräsmattan, vidskogsvägen</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr"/>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>111773558</v>
+        <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>105155</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90290</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220107</v>
+        <v>6286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752974</v>
+        <v>753398</v>
       </c>
       <c r="R132" t="n">
-        <v>7095000</v>
+        <v>7095650</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15520,12 +15473,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15534,84 +15487,66 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126953776</v>
+        <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>56619</v>
+        <v>92760</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>208260</v>
+        <v>4365</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>752974</v>
+        <v>753522</v>
       </c>
       <c r="R133" t="n">
-        <v>7095000</v>
+        <v>7095689</v>
       </c>
       <c r="S133" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15635,27 +15570,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Mörk med tydligt zig zag band - 72 cm.</t>
+          <t>Under tunn tallåga, grenhög</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15664,84 +15589,66 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127009098</v>
+        <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>58494</v>
+        <v>92760</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>208245</v>
+        <v>4365</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>752974</v>
+        <v>753106</v>
       </c>
       <c r="R134" t="n">
-        <v>7095000</v>
+        <v>7095389</v>
       </c>
       <c r="S134" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15765,22 +15672,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, återfynd från 2024</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15789,22 +15691,743 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128787986</v>
+      </c>
+      <c r="B135" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>753392</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7095478</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128787985</v>
+      </c>
+      <c r="B136" t="n">
+        <v>90093</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>753179</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7095384</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1736026</v>
+      </c>
+      <c r="B137" t="n">
+        <v>76579</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>4202</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Svart jordtunga</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Geoglossum umbratile</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Kulla, Vb</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>752996.3043383379</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7095001.956038775</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2012-09-22</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>i gräsmattan, vidskogsvägen</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr"/>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>111773558</v>
+      </c>
+      <c r="B138" t="n">
+        <v>105155</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S138" t="n">
+        <v>50</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
           <t>Bertil Brånin</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
+      <c r="AX138" t="inlineStr">
         <is>
           <t>Bertil Brånin</t>
         </is>
       </c>
-      <c r="AY134" t="inlineStr"/>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>126953776</v>
+      </c>
+      <c r="B139" t="n">
+        <v>56619</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S139" t="n">
+        <v>50</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Mörk med tydligt zig zag band - 72 cm.</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>127009098</v>
+      </c>
+      <c r="B140" t="n">
+        <v>58494</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S140" t="n">
+        <v>50</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>128464803</v>
       </c>
       <c r="B130" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90290</v>
+        <v>90317</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>128787986</v>
       </c>
       <c r="B135" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90093</v>
+        <v>90120</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90317</v>
+        <v>90322</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90120</v>
+        <v>90125</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90322</v>
+        <v>90327</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90125</v>
+        <v>90130</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY140"/>
+  <dimension ref="A1:AY141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15925,59 +15925,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1736026</v>
+        <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>76579</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92798</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4202</v>
+        <v>4365</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sacc.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>KåddisKulla, Vb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>752996.3043383379</v>
+        <v>753174</v>
       </c>
       <c r="R137" t="n">
-        <v>7095001.956038775</v>
+        <v>7095546</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16004,22 +15990,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2012-11-23</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Under tallåga</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16031,36 +16012,25 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>i gräsmattan, vidskogsvägen</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr"/>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>111773558</v>
+        <v>1736026</v>
       </c>
       <c r="B138" t="n">
-        <v>105155</v>
+        <v>76579</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16069,57 +16039,50 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220107</v>
+        <v>4202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Geoglossum umbratile</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sacc.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752974</v>
+        <v>752996.3043383379</v>
       </c>
       <c r="R138" t="n">
-        <v>7095000</v>
+        <v>7095001.956038775</v>
       </c>
       <c r="S138" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16143,12 +16106,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2012-09-22</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16157,70 +16130,84 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>i gräsmattan, vidskogsvägen</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr"/>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Nada Lipovac</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Nada Lipovac</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126953776</v>
+        <v>111773558</v>
       </c>
       <c r="B139" t="n">
-        <v>56619</v>
+        <v>105155</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>208260</v>
+        <v>220107</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Klofibbla</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Crepis tectorum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -16258,27 +16245,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Mörk med tydligt zig zag band - 72 cm.</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16306,10 +16278,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127009098</v>
+        <v>126953776</v>
       </c>
       <c r="B140" t="n">
-        <v>58494</v>
+        <v>56619</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16317,16 +16289,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>208245</v>
+        <v>208260</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -16388,22 +16360,27 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Mörk med tydligt zig zag band - 72 cm.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16428,6 +16405,131 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>127009098</v>
+      </c>
+      <c r="B141" t="n">
+        <v>58494</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S141" t="n">
+        <v>50</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>128464803</v>
       </c>
       <c r="B130" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90327</v>
+        <v>90331</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>128787986</v>
       </c>
       <c r="B135" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90130</v>
+        <v>90134</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14982,7 +14982,7 @@
         <v>128464818</v>
       </c>
       <c r="B128" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>128464817</v>
       </c>
       <c r="B129" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>128464803</v>
       </c>
       <c r="B130" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90331</v>
+        <v>90336</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>128787986</v>
       </c>
       <c r="B135" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90134</v>
+        <v>90139</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -10498,12 +10498,7 @@
         <v>120673188</v>
       </c>
       <c r="B88" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57883</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -15300,7 +15300,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90343</v>
+        <v>90346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90146</v>
+        <v>90149</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -15300,7 +15300,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90346</v>
+        <v>90349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90149</v>
+        <v>90152</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -10498,7 +10498,7 @@
         <v>120673188</v>
       </c>
       <c r="B88" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90349</v>
+        <v>90353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>128787986</v>
       </c>
       <c r="B135" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -15300,7 +15300,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90353</v>
+        <v>90360</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90156</v>
+        <v>90163</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -10498,7 +10498,7 @@
         <v>120673188</v>
       </c>
       <c r="B88" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90360</v>
+        <v>90362</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>128787986</v>
       </c>
       <c r="B135" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90163</v>
+        <v>90165</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -15300,7 +15300,7 @@
         <v>128787965</v>
       </c>
       <c r="B131" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>128787941</v>
       </c>
       <c r="B132" t="n">
-        <v>90362</v>
+        <v>90363</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>128787962</v>
       </c>
       <c r="B133" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>128787963</v>
       </c>
       <c r="B134" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>128787985</v>
       </c>
       <c r="B136" t="n">
-        <v>90165</v>
+        <v>90166</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -15923,7 +15923,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -15923,7 +15923,7 @@
         <v>128937599</v>
       </c>
       <c r="B137" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -14740,7 +14740,7 @@
         <v>127073715</v>
       </c>
       <c r="B126" t="n">
-        <v>88428</v>
+        <v>88406</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>127074261</v>
       </c>
       <c r="B127" t="n">
-        <v>57826</v>
+        <v>57817</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>126953776</v>
       </c>
       <c r="B140" t="n">
-        <v>56619</v>
+        <v>56613</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>127009098</v>
       </c>
       <c r="B141" t="n">
-        <v>58494</v>
+        <v>58488</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY179"/>
+  <dimension ref="A1:AZ179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/292859</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104182920</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127073715</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127261841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/147546</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549601</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119222031</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1788,6 +1838,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/445647</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1900,6 +1955,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119571906</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2017,6 +2077,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533210</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2134,6 +2199,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533211</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2251,6 +2321,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533214</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2348,6 +2423,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246144</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2455,6 +2535,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112013651</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2562,6 +2647,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673692</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2679,6 +2769,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729339</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2790,6 +2885,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1099353</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2887,6 +2987,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246126</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2984,6 +3089,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246130</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3081,6 +3191,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246147</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3178,6 +3293,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549598</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3275,6 +3395,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549608</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3372,6 +3497,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642921</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3469,6 +3599,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642922</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3566,6 +3701,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642925</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3673,6 +3813,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112013655</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3780,6 +3925,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112013657</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3887,6 +4037,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112013658</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4008,6 +4163,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119222149</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4119,6 +4279,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119587444</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4230,6 +4395,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119587452</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4346,6 +4516,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119587701</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4462,6 +4637,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119587815</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4559,6 +4739,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718996</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4660,6 +4845,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533237</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4761,6 +4951,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533238</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4868,6 +5063,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673850</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4974,6 +5174,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729370</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5093,6 +5298,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99497515</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5190,6 +5400,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246142</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5287,6 +5502,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246149</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5384,6 +5604,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246156</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5481,6 +5706,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549606</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5588,6 +5818,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112013678</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5695,6 +5930,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112013679</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5811,6 +6051,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119222184</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5922,6 +6167,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119587537</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6033,6 +6283,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119587841</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6140,6 +6395,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120674352</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6247,6 +6507,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677293</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6354,6 +6619,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677588</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6451,6 +6721,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246128</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6548,6 +6823,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246129</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6645,6 +6925,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246141</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6742,6 +7027,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246151</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6839,6 +7129,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246153</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6936,6 +7231,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246155</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7033,6 +7333,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246157</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7130,6 +7435,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246158</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7227,6 +7537,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246160</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7324,6 +7639,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549604</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7421,6 +7741,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549609</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7518,6 +7843,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642939</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7615,6 +7945,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642941</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7712,6 +8047,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642942</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7814,6 +8154,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533244</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7911,6 +8256,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533245</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8008,6 +8358,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533246</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8105,6 +8460,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533247</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8212,6 +8572,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673420</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8319,6 +8684,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673517</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8426,6 +8796,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673615</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8533,6 +8908,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673644</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8640,6 +9020,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673663</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8747,6 +9132,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673694</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8854,6 +9244,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673838</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8961,6 +9356,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120674959</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9068,6 +9468,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120675872</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9175,6 +9580,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677032</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9282,6 +9692,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677072</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9384,6 +9799,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729383</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9481,6 +9901,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729384</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9578,6 +10003,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729385</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9675,6 +10105,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729386</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9772,6 +10207,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729387</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9869,6 +10309,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729388</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9966,6 +10411,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729389</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10068,6 +10518,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464817</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10170,6 +10625,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464818</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10276,6 +10736,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464819</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10378,6 +10843,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533224</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10480,6 +10950,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533225</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10582,6 +11057,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533226</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10684,6 +11164,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533227</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10786,6 +11271,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533228</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10888,6 +11378,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533229</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10994,6 +11489,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533231</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11100,6 +11600,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533232</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11207,6 +11712,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120676219</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11314,6 +11824,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120676690</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11416,6 +11931,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729360</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11518,6 +12038,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729361</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11620,6 +12145,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729362</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11722,6 +12252,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729363</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11828,6 +12363,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729364</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11930,6 +12470,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787962</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12032,6 +12577,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787963</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12134,6 +12684,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787965</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12236,6 +12791,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128937599</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12333,6 +12893,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246127</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12430,6 +12995,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246143</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12527,6 +13097,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246145</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12624,6 +13199,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246150</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12721,6 +13301,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246159</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12818,6 +13403,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246186</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12915,6 +13505,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246187</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13012,6 +13607,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642918</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13109,6 +13709,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642919</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13216,6 +13821,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120674846</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13333,6 +13943,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1667764</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13440,6 +14055,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1197762</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13551,6 +14171,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1226779</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13664,6 +14289,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1256425</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13761,6 +14391,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642906</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13862,6 +14497,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787985</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13989,6 +14629,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110217658</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14090,6 +14735,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533239</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14187,6 +14837,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533241</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14294,6 +14949,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673249</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14401,6 +15061,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673747</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14508,6 +15173,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120675378</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14615,6 +15285,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120675392</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14722,6 +15397,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677239</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14823,6 +15503,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729371</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14929,6 +15614,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533222</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15031,6 +15721,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128761110</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15155,6 +15850,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974116</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15252,6 +15952,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246131</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15349,6 +16054,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246146</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15446,6 +16156,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246152</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15543,6 +16258,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246154</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15640,6 +16360,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103246188</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15737,6 +16462,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549610</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15834,6 +16564,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642933</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15931,6 +16666,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111642934</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16038,6 +16778,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112013672</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16154,6 +16899,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119587687</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16264,6 +17014,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549603</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16365,6 +17120,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787941</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16492,6 +17252,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533219</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16619,6 +17384,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533220</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16746,6 +17516,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120533221</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16858,6 +17633,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673729</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16980,6 +17760,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729356</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17102,6 +17887,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729357</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17224,6 +18014,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729358</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17346,6 +18141,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729359</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17448,6 +18248,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103549599</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17553,6 +18358,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729372</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17658,6 +18468,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120729373</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17765,6 +18580,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673188</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17872,6 +18692,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120675156</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17979,6 +18804,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120676556</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18098,6 +18928,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120692477</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18214,6 +19049,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127074261</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18333,6 +19173,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128464803</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18448,6 +19293,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128787986</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18545,6 +19395,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718999</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18661,6 +19516,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119587677</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18778,6 +19638,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1718088</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18895,6 +19760,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1736026</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19006,6 +19876,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119682500</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19123,6 +19998,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1298981</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19248,6 +20128,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127009098</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19378,6 +20263,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126953776</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19492,8 +20382,193 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111773558</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -5185,7 +5185,7 @@
         <v>136356702</v>
       </c>
       <c r="B42" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136356995</v>
       </c>
       <c r="B56" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>136356269</v>
       </c>
       <c r="B96" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>136356315</v>
       </c>
       <c r="B97" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>136356351</v>
       </c>
       <c r="B98" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>136356430</v>
       </c>
       <c r="B99" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>136357307</v>
       </c>
       <c r="B100" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136357556</v>
       </c>
       <c r="B101" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>136358081</v>
       </c>
       <c r="B102" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>136358182</v>
       </c>
       <c r="B122" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>136359040</v>
       </c>
       <c r="B123" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>136356211</v>
       </c>
       <c r="B141" t="n">
-        <v>93407</v>
+        <v>93414</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>136357506</v>
       </c>
       <c r="B142" t="n">
-        <v>93407</v>
+        <v>93414</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>136358191</v>
       </c>
       <c r="B143" t="n">
-        <v>93407</v>
+        <v>93414</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>136358859</v>
       </c>
       <c r="B154" t="n">
-        <v>93362</v>
+        <v>93369</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>136357484</v>
       </c>
       <c r="B186" t="n">
-        <v>106444</v>
+        <v>106457</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>136358853</v>
       </c>
       <c r="B187" t="n">
-        <v>93409</v>
+        <v>93416</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -5185,7 +5185,7 @@
         <v>136356702</v>
       </c>
       <c r="B42" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136356995</v>
       </c>
       <c r="B56" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>136356269</v>
       </c>
       <c r="B96" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>136356315</v>
       </c>
       <c r="B97" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>136356351</v>
       </c>
       <c r="B98" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>136356430</v>
       </c>
       <c r="B99" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>136357307</v>
       </c>
       <c r="B100" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136357556</v>
       </c>
       <c r="B101" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>136358081</v>
       </c>
       <c r="B102" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>136358182</v>
       </c>
       <c r="B122" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>136359040</v>
       </c>
       <c r="B123" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>136356211</v>
       </c>
       <c r="B141" t="n">
-        <v>93414</v>
+        <v>93415</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>136357506</v>
       </c>
       <c r="B142" t="n">
-        <v>93414</v>
+        <v>93415</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>136358191</v>
       </c>
       <c r="B143" t="n">
-        <v>93414</v>
+        <v>93415</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>136358859</v>
       </c>
       <c r="B154" t="n">
-        <v>93369</v>
+        <v>93370</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>136357484</v>
       </c>
       <c r="B186" t="n">
-        <v>106457</v>
+        <v>106458</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>136358853</v>
       </c>
       <c r="B187" t="n">
-        <v>93416</v>
+        <v>93417</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -5185,7 +5185,7 @@
         <v>136356702</v>
       </c>
       <c r="B42" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136356995</v>
       </c>
       <c r="B56" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136455202</v>
       </c>
       <c r="B57" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>136356269</v>
       </c>
       <c r="B97" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>136356315</v>
       </c>
       <c r="B98" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>136356351</v>
       </c>
       <c r="B99" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>136356430</v>
       </c>
       <c r="B100" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>136357307</v>
       </c>
       <c r="B101" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>136357556</v>
       </c>
       <c r="B102" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>136358081</v>
       </c>
       <c r="B103" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>136455012</v>
       </c>
       <c r="B104" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>136455283</v>
       </c>
       <c r="B105" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136455805</v>
       </c>
       <c r="B106" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>136358182</v>
       </c>
       <c r="B126" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>136359040</v>
       </c>
       <c r="B127" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>136356211</v>
       </c>
       <c r="B145" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>136357506</v>
       </c>
       <c r="B146" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>136358191</v>
       </c>
       <c r="B147" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>136358859</v>
       </c>
       <c r="B158" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>136357484</v>
       </c>
       <c r="B190" t="n">
-        <v>106471</v>
+        <v>106472</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>136358853</v>
       </c>
       <c r="B191" t="n">
-        <v>93430</v>
+        <v>93431</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
